--- a/ig/DM-JUILLET-2026/CodeSystem-TRE-R344-NiveauExpertise.xlsx
+++ b/ig/DM-JUILLET-2026/CodeSystem-TRE-R344-NiveauExpertise.xlsx
@@ -118,291 +118,294 @@
     <t>Count</t>
   </si>
   <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Uri</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>dateValid</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
+  </si>
+  <si>
+    <t>date de validité d'un code concept</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>dateMaj</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
+  </si>
+  <si>
+    <t>Date de mise à jour d'un code concept</t>
+  </si>
+  <si>
+    <t>dateFin</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
+  </si>
+  <si>
+    <t>Date de fin d'exploitation d'un code concept</t>
+  </si>
+  <si>
+    <t>deprecationDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
+  </si>
+  <si>
+    <t>Date Concept was deprecated</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>A property that indicates the status of the concept.</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>retirementDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
+  </si>
+  <si>
+    <t>Date Concept was retired</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Centre de référence labellisé</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Centre de compétences labellisé</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Structure spécialisée labellisée</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation des personnes en état de conscience altérée</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation des patients amputés, appareillés ou non</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation PREcoce Post-Aiguë Cardiologique (PREPAC)</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation PREcoce Post-Aiguë Respiratoire (PREPAR)</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation neuro-orthopédique</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation post-réanimation (SRPR)</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation PREcoce Post-Aiguë Neurologique (PREPAN)</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation des troubles des patients cérébro-lésés</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation des lésions médullaires</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation des obésités complexes</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation troubles cognitifs liés à une conduite addictive</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation du polyhandicap</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation des troubles du langage et des apprentissages</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Centre de recours pour chirurgie oncologique complexe</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Premier niveau de recours</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Deuxième niveau de recours</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Troisième niveau de recours</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Unité de réanimation pédiatrique de recours</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Filière endométriose - premier niveau de recours</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Filière endométriose - deuxième niveau de recours</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Filière endométriose - troisième niveau de recours</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Centre labellisé Covid-Long</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>Centre de réhabilitation psychosociale - Centre de recours labellisé</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>Centre de réhabilitation psychosociale - Centre de proximité labellisé</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>Unité neuro-vasculaire (UNV) de territoire</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Unité neuro-vasculaire (UNV) de recours</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>Filière Obésité - Niveau 1 Conventionné Centres Spécialisés Obésité (CSO)</t>
+  </si>
+  <si>
+    <t>Intervention de premier niveau de recours dans la filière de soin coordonnée obésité, devant être conventionnée avec un centre spécialisé obésité (CSO).</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Filière Obésité - Niveau 2 Conventionné Centres Spécialisés Obésité (CSO)</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Filière Obésité - Niveau 3 Conventionné Centres Spécialisés Obésité (CSO)</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Filière Obésité - Niveau 3 (Centre Spécialisé Obésité)</t>
+  </si>
+  <si>
     <t>43</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Uri</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>dateValid</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
-  </si>
-  <si>
-    <t>date de validité d'un code concept</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>dateMaj</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
-  </si>
-  <si>
-    <t>Date de mise à jour d'un code concept</t>
-  </si>
-  <si>
-    <t>dateFin</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
-  </si>
-  <si>
-    <t>Date de fin d'exploitation d'un code concept</t>
-  </si>
-  <si>
-    <t>deprecationDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
-  </si>
-  <si>
-    <t>Date Concept was deprecated</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#status</t>
-  </si>
-  <si>
-    <t>A property that indicates the status of the concept.</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>retirementDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
-  </si>
-  <si>
-    <t>Date Concept was retired</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Centre de référence labellisé</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Centre de compétences labellisé</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Structure spécialisée labellisée</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation des personnes en état de conscience altérée</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation des patients amputés, appareillés ou non</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation PREcoce Post-Aiguë Cardiologique (PREPAC)</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation PREcoce Post-Aiguë Respiratoire (PREPAR)</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation neuro-orthopédique</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation post-réanimation (SRPR)</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation PREcoce Post-Aiguë Neurologique (PREPAN)</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation des troubles des patients cérébro-lésés</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation des lésions médullaires</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation des obésités complexes</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation troubles cognitifs liés à une conduite addictive</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation du polyhandicap</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation des troubles du langage et des apprentissages</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Centre de recours pour chirurgie oncologique complexe</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>Premier niveau de recours</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>Deuxième niveau de recours</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>Troisième niveau de recours</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>Unité de réanimation pédiatrique de recours</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>Filière endométriose - premier niveau de recours</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>Filière endométriose - deuxième niveau de recours</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>Filière endométriose - troisième niveau de recours</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>Centre labellisé Covid-Long</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>Centre de réhabilitation psychosociale - Centre de recours labellisé</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>Centre de réhabilitation psychosociale - Centre de proximité labellisé</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>Unité neuro-vasculaire (UNV) de territoire</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>Unité neuro-vasculaire (UNV) de recours</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>Filière Obésité - Niveau 1 Conventionné Centres Spécialisés Obésité (CSO)</t>
-  </si>
-  <si>
-    <t>Intervention de premier niveau de recours dans la filière de soin coordonnée obésité, devant être conventionnée avec un centre spécialisé obésité (CSO).</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Filière Obésité - Niveau 2 Conventionné Centres Spécialisés Obésité (CSO)</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>Filière Obésité - Niveau 3 Conventionné Centres Spécialisés Obésité (CSO)</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>Filière Obésité - Niveau 3 (Centre Spécialisé Obésité)</t>
-  </si>
-  <si>
     <t>Centre Ressources Autisme (CRA)</t>
   </si>
   <si>
@@ -416,9 +419,6 @@
   </si>
   <si>
     <t>Centre de référence du Trouble Déficit de l’Attention avec ou sans Hyperactivité (CRTDAH)</t>
-  </si>
-  <si>
-    <t>46</t>
   </si>
   <si>
     <t>Centre de compétence centre mémoire ressources et recherche (CMRR)</t>
@@ -1311,10 +1311,10 @@
         <v>61</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D35" s="2"/>
     </row>
@@ -1323,10 +1323,10 @@
         <v>61</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D36" s="2"/>
     </row>
@@ -1335,10 +1335,10 @@
         <v>61</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D37" s="2"/>
     </row>
@@ -1347,7 +1347,7 @@
         <v>61</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>134</v>
+        <v>34</v>
       </c>
       <c r="C38" t="s" s="2">
         <v>135</v>
